--- a/Output Files DeepSeek V4 Flash/LLM-Parameterized_Reference_Scoring_results_run_02.xlsx
+++ b/Output Files DeepSeek V4 Flash/LLM-Parameterized_Reference_Scoring_results_run_02.xlsx
@@ -39077,7 +39077,7 @@
         <v>3</v>
       </c>
       <c r="AD407" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="408">
@@ -39359,7 +39359,7 @@
         <v>2</v>
       </c>
       <c r="AD410" t="n">
-        <v>0.8194999999999999</v>
+        <v>0.8195</v>
       </c>
     </row>
     <row r="411">
@@ -39829,7 +39829,7 @@
         <v>3</v>
       </c>
       <c r="AD415" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="416">
@@ -40478,7 +40478,7 @@
         <v>0.83</v>
       </c>
       <c r="AA422" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="AB422" t="n">
         <v>0.5</v>
@@ -40487,7 +40487,7 @@
         <v>1</v>
       </c>
       <c r="AD422" t="n">
-        <v>0.7234999999999999</v>
+        <v>0.7415</v>
       </c>
     </row>
     <row r="423">
@@ -40572,7 +40572,7 @@
         <v>0.67</v>
       </c>
       <c r="AA423" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="AB423" t="n">
         <v>0.52</v>
@@ -40581,7 +40581,7 @@
         <v>2</v>
       </c>
       <c r="AD423" t="n">
-        <v>0.6455</v>
+        <v>0.6695</v>
       </c>
     </row>
     <row r="424">
@@ -40666,7 +40666,7 @@
         <v>0.51</v>
       </c>
       <c r="AA424" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="AB424" t="n">
         <v>0.67</v>
@@ -40675,7 +40675,7 @@
         <v>3</v>
       </c>
       <c r="AD424" t="n">
-        <v>0.537</v>
+        <v>0.571</v>
       </c>
     </row>
     <row r="425">
@@ -40760,7 +40760,7 @@
         <v>0.96</v>
       </c>
       <c r="AA425" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="AB425" t="n">
         <v>0.35</v>
@@ -40769,7 +40769,7 @@
         <v>3</v>
       </c>
       <c r="AD425" t="n">
-        <v>0.7775</v>
+        <v>0.7955</v>
       </c>
     </row>
     <row r="426">
@@ -40854,7 +40854,7 @@
         <v>0.88</v>
       </c>
       <c r="AA426" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB426" t="n">
         <v>0.64</v>
@@ -40863,7 +40863,7 @@
         <v>1</v>
       </c>
       <c r="AD426" t="n">
-        <v>0.7959999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
     </row>
     <row r="427">
@@ -40948,7 +40948,7 @@
         <v>0.77</v>
       </c>
       <c r="AA427" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB427" t="n">
         <v>0.85</v>
@@ -40957,7 +40957,7 @@
         <v>2</v>
       </c>
       <c r="AD427" t="n">
-        <v>0.788</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="428">
@@ -41051,7 +41051,7 @@
         <v>1</v>
       </c>
       <c r="AD428" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="429">
@@ -41230,7 +41230,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="AA430" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="AB430" t="n">
         <v>0.52</v>
@@ -41239,7 +41239,7 @@
         <v>2</v>
       </c>
       <c r="AD430" t="n">
-        <v>0.7585</v>
+        <v>0.7665</v>
       </c>
     </row>
     <row r="431">
@@ -41324,7 +41324,7 @@
         <v>0.83</v>
       </c>
       <c r="AA431" t="n">
-        <v>0.66</v>
+        <v>0.74</v>
       </c>
       <c r="AB431" t="n">
         <v>0.35</v>
@@ -41333,7 +41333,7 @@
         <v>1</v>
       </c>
       <c r="AD431" t="n">
-        <v>0.742</v>
+        <v>0.758</v>
       </c>
     </row>
     <row r="432">
@@ -41418,7 +41418,7 @@
         <v>0.64</v>
       </c>
       <c r="AA432" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="AB432" t="n">
         <v>0.46</v>
@@ -41427,7 +41427,7 @@
         <v>2</v>
       </c>
       <c r="AD432" t="n">
-        <v>0.6990000000000001</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="433">
@@ -41512,7 +41512,7 @@
         <v>0.38</v>
       </c>
       <c r="AA433" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="AB433" t="n">
         <v>0.67</v>
@@ -41521,7 +41521,7 @@
         <v>3</v>
       </c>
       <c r="AD433" t="n">
-        <v>0.5285</v>
+        <v>0.5445</v>
       </c>
     </row>
     <row r="434">
@@ -41606,7 +41606,7 @@
         <v>0.64</v>
       </c>
       <c r="AA434" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="AB434" t="n">
         <v>0.46</v>
@@ -41615,7 +41615,7 @@
         <v>1</v>
       </c>
       <c r="AD434" t="n">
-        <v>0.6100000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="435">
@@ -41700,7 +41700,7 @@
         <v>0.38</v>
       </c>
       <c r="AA435" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="AB435" t="n">
         <v>0.67</v>
@@ -41709,7 +41709,7 @@
         <v>2</v>
       </c>
       <c r="AD435" t="n">
-        <v>0.4465</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="436">
@@ -41794,7 +41794,7 @@
         <v>0.13</v>
       </c>
       <c r="AA436" t="n">
-        <v>0.34</v>
+        <v>0.58</v>
       </c>
       <c r="AB436" t="n">
         <v>0.48</v>
@@ -41803,7 +41803,7 @@
         <v>3</v>
       </c>
       <c r="AD436" t="n">
-        <v>0.1855</v>
+        <v>0.2335</v>
       </c>
     </row>
     <row r="437">
@@ -41888,7 +41888,7 @@
         <v>0.51</v>
       </c>
       <c r="AA437" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="AB437" t="n">
         <v>0.57</v>
@@ -41897,7 +41897,7 @@
         <v>1</v>
       </c>
       <c r="AD437" t="n">
-        <v>0.618</v>
+        <v>0.632</v>
       </c>
     </row>
     <row r="438">
@@ -41982,7 +41982,7 @@
         <v>0.19</v>
       </c>
       <c r="AA438" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="AB438" t="n">
         <v>0.52</v>
@@ -41991,7 +41991,7 @@
         <v>2</v>
       </c>
       <c r="AD438" t="n">
-        <v>0.3485</v>
+        <v>0.3685</v>
       </c>
     </row>
     <row r="439">
@@ -42076,7 +42076,7 @@
         <v>0</v>
       </c>
       <c r="AA439" t="n">
-        <v>0.06</v>
+        <v>0.21</v>
       </c>
       <c r="AB439" t="n">
         <v>0.4</v>
@@ -42085,7 +42085,7 @@
         <v>3</v>
       </c>
       <c r="AD439" t="n">
-        <v>0.141</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="440">
@@ -42170,7 +42170,7 @@
         <v>0.77</v>
       </c>
       <c r="AA440" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="AB440" t="n">
         <v>0.5</v>
@@ -42179,7 +42179,7 @@
         <v>1</v>
       </c>
       <c r="AD440" t="n">
-        <v>0.6814999999999999</v>
+        <v>0.6995</v>
       </c>
     </row>
     <row r="441">
@@ -42264,7 +42264,7 @@
         <v>0.51</v>
       </c>
       <c r="AA441" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="AB441" t="n">
         <v>0.57</v>
@@ -42273,7 +42273,7 @@
         <v>2</v>
       </c>
       <c r="AD441" t="n">
-        <v>0.546</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="442">
@@ -42358,7 +42358,7 @@
         <v>0.19</v>
       </c>
       <c r="AA442" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AB442" t="n">
         <v>0.52</v>
@@ -42367,7 +42367,7 @@
         <v>3</v>
       </c>
       <c r="AD442" t="n">
-        <v>0.2375</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="443">
@@ -42555,7 +42555,7 @@
         <v>2</v>
       </c>
       <c r="AD444" t="n">
-        <v>0.7364999999999999</v>
+        <v>0.7365</v>
       </c>
     </row>
     <row r="445">
@@ -42734,7 +42734,7 @@
         <v>0.77</v>
       </c>
       <c r="AA446" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="AB446" t="n">
         <v>0.15</v>
@@ -42743,7 +42743,7 @@
         <v>1</v>
       </c>
       <c r="AD446" t="n">
-        <v>0.6289999999999999</v>
+        <v>0.647</v>
       </c>
     </row>
     <row r="447">
@@ -42828,7 +42828,7 @@
         <v>0.51</v>
       </c>
       <c r="AA447" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="AB447" t="n">
         <v>0.57</v>
@@ -42837,7 +42837,7 @@
         <v>2</v>
       </c>
       <c r="AD447" t="n">
-        <v>0.546</v>
+        <v>0.574</v>
       </c>
     </row>
     <row r="448">
@@ -42922,7 +42922,7 @@
         <v>0.19</v>
       </c>
       <c r="AA448" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AB448" t="n">
         <v>0.52</v>
@@ -42931,7 +42931,7 @@
         <v>3</v>
       </c>
       <c r="AD448" t="n">
-        <v>0.2375</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="449">
@@ -43016,7 +43016,7 @@
         <v>0.71</v>
       </c>
       <c r="AA449" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="AB449" t="n">
         <v>0.64</v>
@@ -43025,7 +43025,7 @@
         <v>1</v>
       </c>
       <c r="AD449" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.7675</v>
       </c>
     </row>
     <row r="450">
@@ -43110,7 +43110,7 @@
         <v>0.38</v>
       </c>
       <c r="AA450" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="AB450" t="n">
         <v>0.67</v>
@@ -43119,7 +43119,7 @@
         <v>2</v>
       </c>
       <c r="AD450" t="n">
-        <v>0.5625</v>
+        <v>0.5765</v>
       </c>
     </row>
     <row r="451">
@@ -43204,7 +43204,7 @@
         <v>0.13</v>
       </c>
       <c r="AA451" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="AB451" t="n">
         <v>0.48</v>
@@ -43213,7 +43213,7 @@
         <v>3</v>
       </c>
       <c r="AD451" t="n">
-        <v>0.3645</v>
+        <v>0.3805</v>
       </c>
     </row>
     <row r="452">
@@ -43298,7 +43298,7 @@
         <v>0.38</v>
       </c>
       <c r="AA452" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="AB452" t="n">
         <v>0.67</v>
@@ -43307,7 +43307,7 @@
         <v>1</v>
       </c>
       <c r="AD452" t="n">
-        <v>0.4465</v>
+        <v>0.4805</v>
       </c>
     </row>
     <row r="453">
@@ -43392,7 +43392,7 @@
         <v>0.19</v>
       </c>
       <c r="AA453" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AB453" t="n">
         <v>0.52</v>
@@ -43401,7 +43401,7 @@
         <v>2</v>
       </c>
       <c r="AD453" t="n">
-        <v>0.2375</v>
+        <v>0.2815</v>
       </c>
     </row>
     <row r="454">
@@ -43486,7 +43486,7 @@
         <v>0</v>
       </c>
       <c r="AA454" t="n">
-        <v>0.06</v>
+        <v>0.36</v>
       </c>
       <c r="AB454" t="n">
         <v>0.4</v>
@@ -43495,7 +43495,7 @@
         <v>3</v>
       </c>
       <c r="AD454" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="455">
@@ -43683,7 +43683,7 @@
         <v>1</v>
       </c>
       <c r="AD456" t="n">
-        <v>0.8815000000000001</v>
+        <v>0.8815</v>
       </c>
     </row>
     <row r="457">
@@ -43777,7 +43777,7 @@
         <v>3</v>
       </c>
       <c r="AD457" t="n">
-        <v>0.7989999999999999</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="458">
@@ -43862,7 +43862,7 @@
         <v>0.51</v>
       </c>
       <c r="AA458" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="AB458" t="n">
         <v>0.57</v>
@@ -43871,7 +43871,7 @@
         <v>1</v>
       </c>
       <c r="AD458" t="n">
-        <v>0.618</v>
+        <v>0.632</v>
       </c>
     </row>
     <row r="459">
@@ -43956,7 +43956,7 @@
         <v>0.26</v>
       </c>
       <c r="AA459" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="AB459" t="n">
         <v>0.57</v>
@@ -43965,7 +43965,7 @@
         <v>2</v>
       </c>
       <c r="AD459" t="n">
-        <v>0.4115</v>
+        <v>0.4315</v>
       </c>
     </row>
     <row r="460">
@@ -44050,7 +44050,7 @@
         <v>0</v>
       </c>
       <c r="AA460" t="n">
-        <v>0.06</v>
+        <v>0.21</v>
       </c>
       <c r="AB460" t="n">
         <v>0.4</v>
@@ -44059,7 +44059,7 @@
         <v>3</v>
       </c>
       <c r="AD460" t="n">
-        <v>0.141</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="461">
@@ -44153,7 +44153,7 @@
         <v>3</v>
       </c>
       <c r="AD461" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="462">
@@ -44247,7 +44247,7 @@
         <v>2</v>
       </c>
       <c r="AD462" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="463">
@@ -44623,7 +44623,7 @@
         <v>3</v>
       </c>
       <c r="AD466" t="n">
-        <v>0.7129999999999999</v>
+        <v>0.713</v>
       </c>
     </row>
     <row r="467">
@@ -44708,7 +44708,7 @@
         <v>0.74</v>
       </c>
       <c r="AA467" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="AB467" t="n">
         <v>0.46</v>
@@ -44717,7 +44717,7 @@
         <v>1</v>
       </c>
       <c r="AD467" t="n">
-        <v>0.6839999999999999</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="468">
@@ -44802,7 +44802,7 @@
         <v>0.54</v>
       </c>
       <c r="AA468" t="n">
-        <v>0.72</v>
+        <v>0.89</v>
       </c>
       <c r="AB468" t="n">
         <v>0.67</v>
@@ -44811,7 +44811,7 @@
         <v>2</v>
       </c>
       <c r="AD468" t="n">
-        <v>0.5565</v>
+        <v>0.5905</v>
       </c>
     </row>
     <row r="469">
@@ -44896,7 +44896,7 @@
         <v>0.38</v>
       </c>
       <c r="AA469" t="n">
-        <v>0.45</v>
+        <v>0.67</v>
       </c>
       <c r="AB469" t="n">
         <v>0.52</v>
@@ -44905,7 +44905,7 @@
         <v>3</v>
       </c>
       <c r="AD469" t="n">
-        <v>0.37</v>
+        <v>0.414</v>
       </c>
     </row>
     <row r="470">
@@ -45093,7 +45093,7 @@
         <v>1</v>
       </c>
       <c r="AD471" t="n">
-        <v>0.8815000000000001</v>
+        <v>0.8815</v>
       </c>
     </row>
     <row r="472">
@@ -45187,7 +45187,7 @@
         <v>3</v>
       </c>
       <c r="AD472" t="n">
-        <v>0.7989999999999999</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="473">
@@ -45272,7 +45272,7 @@
         <v>0.83</v>
       </c>
       <c r="AA473" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="AB473" t="n">
         <v>0.35</v>
@@ -45281,7 +45281,7 @@
         <v>1</v>
       </c>
       <c r="AD473" t="n">
-        <v>0.6869999999999999</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="474">
@@ -45366,7 +45366,7 @@
         <v>0.64</v>
       </c>
       <c r="AA474" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="AB474" t="n">
         <v>0.76</v>
@@ -45375,7 +45375,7 @@
         <v>2</v>
       </c>
       <c r="AD474" t="n">
-        <v>0.655</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="475">
@@ -45460,7 +45460,7 @@
         <v>0.38</v>
       </c>
       <c r="AA475" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="AB475" t="n">
         <v>0.67</v>
@@ -45469,7 +45469,7 @@
         <v>3</v>
       </c>
       <c r="AD475" t="n">
-        <v>0.4785</v>
+        <v>0.4925</v>
       </c>
     </row>
     <row r="476">
@@ -45563,7 +45563,7 @@
         <v>1</v>
       </c>
       <c r="AD476" t="n">
-        <v>0.7615000000000001</v>
+        <v>0.7615</v>
       </c>
     </row>
     <row r="477">
@@ -45836,7 +45836,7 @@
         <v>0.9</v>
       </c>
       <c r="AA479" t="n">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
       <c r="AB479" t="n">
         <v>0.29</v>
@@ -45845,7 +45845,7 @@
         <v>1</v>
       </c>
       <c r="AD479" t="n">
-        <v>0.7275</v>
+        <v>0.7475000000000001</v>
       </c>
     </row>
     <row r="480">
@@ -45930,7 +45930,7 @@
         <v>0.71</v>
       </c>
       <c r="AA480" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="AB480" t="n">
         <v>0.31</v>
@@ -45939,7 +45939,7 @@
         <v>2</v>
       </c>
       <c r="AD480" t="n">
-        <v>0.657</v>
+        <v>0.673</v>
       </c>
     </row>
     <row r="481">
@@ -46024,7 +46024,7 @@
         <v>0.51</v>
       </c>
       <c r="AA481" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
       <c r="AB481" t="n">
         <v>0.57</v>
@@ -46033,7 +46033,7 @@
         <v>3</v>
       </c>
       <c r="AD481" t="n">
-        <v>0.5880000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="482">
@@ -46127,7 +46127,7 @@
         <v>2</v>
       </c>
       <c r="AD482" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="483">
@@ -46221,7 +46221,7 @@
         <v>1</v>
       </c>
       <c r="AD483" t="n">
-        <v>0.8055000000000001</v>
+        <v>0.8055</v>
       </c>
     </row>
     <row r="484">
@@ -46306,7 +46306,7 @@
         <v>0.58</v>
       </c>
       <c r="AA484" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="AB484" t="n">
         <v>0.52</v>
@@ -46315,7 +46315,7 @@
         <v>3</v>
       </c>
       <c r="AD484" t="n">
-        <v>0.571</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="485">
@@ -46409,7 +46409,7 @@
         <v>1</v>
       </c>
       <c r="AD485" t="n">
-        <v>0.7814999999999999</v>
+        <v>0.7815</v>
       </c>
     </row>
     <row r="486">
@@ -46691,7 +46691,7 @@
         <v>1</v>
       </c>
       <c r="AD488" t="n">
-        <v>0.8064999999999999</v>
+        <v>0.8065</v>
       </c>
     </row>
     <row r="489">
@@ -46776,7 +46776,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA489" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AB489" t="n">
         <v>0.67</v>
@@ -46785,7 +46785,7 @@
         <v>2</v>
       </c>
       <c r="AD489" t="n">
-        <v>0.7010000000000001</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="490">
@@ -46870,7 +46870,7 @@
         <v>0.38</v>
       </c>
       <c r="AA490" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AB490" t="n">
         <v>0.32</v>
@@ -46879,7 +46879,7 @@
         <v>3</v>
       </c>
       <c r="AD490" t="n">
-        <v>0.289</v>
+        <v>0.301</v>
       </c>
     </row>
     <row r="491">
@@ -46973,7 +46973,7 @@
         <v>2</v>
       </c>
       <c r="AD491" t="n">
-        <v>0.7084999999999999</v>
+        <v>0.7085</v>
       </c>
     </row>
     <row r="492">
@@ -47161,7 +47161,7 @@
         <v>3</v>
       </c>
       <c r="AD493" t="n">
-        <v>0.5225000000000001</v>
+        <v>0.5225</v>
       </c>
     </row>
     <row r="494">
@@ -47349,7 +47349,7 @@
         <v>2</v>
       </c>
       <c r="AD495" t="n">
-        <v>0.7959999999999999</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="496">
@@ -47725,7 +47725,7 @@
         <v>3</v>
       </c>
       <c r="AD499" t="n">
-        <v>0.7729999999999999</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="500">
@@ -47810,7 +47810,7 @@
         <v>0.83</v>
       </c>
       <c r="AA500" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="AB500" t="n">
         <v>0.35</v>
@@ -47819,7 +47819,7 @@
         <v>1</v>
       </c>
       <c r="AD500" t="n">
-        <v>0.699</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="501">
@@ -47904,7 +47904,7 @@
         <v>0.64</v>
       </c>
       <c r="AA501" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="AB501" t="n">
         <v>0.46</v>
@@ -47913,7 +47913,7 @@
         <v>2</v>
       </c>
       <c r="AD501" t="n">
-        <v>0.633</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="502">
@@ -47998,7 +47998,7 @@
         <v>0.38</v>
       </c>
       <c r="AA502" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="AB502" t="n">
         <v>0.67</v>
@@ -48007,7 +48007,7 @@
         <v>3</v>
       </c>
       <c r="AD502" t="n">
-        <v>0.5055000000000001</v>
+        <v>0.5195</v>
       </c>
     </row>
     <row r="503">
@@ -48101,7 +48101,7 @@
         <v>2</v>
       </c>
       <c r="AD503" t="n">
-        <v>0.8164999999999999</v>
+        <v>0.8165</v>
       </c>
     </row>
     <row r="504">
@@ -48374,7 +48374,7 @@
         <v>0.83</v>
       </c>
       <c r="AA506" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AB506" t="n">
         <v>0.35</v>
@@ -48383,7 +48383,7 @@
         <v>1</v>
       </c>
       <c r="AD506" t="n">
-        <v>0.712</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="507">
@@ -48468,7 +48468,7 @@
         <v>0.64</v>
       </c>
       <c r="AA507" t="n">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="AB507" t="n">
         <v>0.46</v>
@@ -48477,7 +48477,7 @@
         <v>2</v>
       </c>
       <c r="AD507" t="n">
-        <v>0.653</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="508">
@@ -48562,7 +48562,7 @@
         <v>0.38</v>
       </c>
       <c r="AA508" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AB508" t="n">
         <v>0.67</v>
@@ -48571,7 +48571,7 @@
         <v>3</v>
       </c>
       <c r="AD508" t="n">
-        <v>0.5245</v>
+        <v>0.5385</v>
       </c>
     </row>
     <row r="509">
@@ -48656,7 +48656,7 @@
         <v>0.83</v>
       </c>
       <c r="AA509" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="AB509" t="n">
         <v>0.35</v>
@@ -48665,7 +48665,7 @@
         <v>1</v>
       </c>
       <c r="AD509" t="n">
-        <v>0.704</v>
+        <v>0.722</v>
       </c>
     </row>
     <row r="510">
@@ -48750,7 +48750,7 @@
         <v>0.64</v>
       </c>
       <c r="AA510" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="AB510" t="n">
         <v>0.46</v>
@@ -48759,7 +48759,7 @@
         <v>2</v>
       </c>
       <c r="AD510" t="n">
-        <v>0.6359999999999999</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="511">
@@ -48844,7 +48844,7 @@
         <v>0.38</v>
       </c>
       <c r="AA511" t="n">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="AB511" t="n">
         <v>0.67</v>
@@ -48853,7 +48853,7 @@
         <v>3</v>
       </c>
       <c r="AD511" t="n">
-        <v>0.4805</v>
+        <v>0.5125</v>
       </c>
     </row>
     <row r="512">
@@ -48938,7 +48938,7 @@
         <v>0.64</v>
       </c>
       <c r="AA512" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AB512" t="n">
         <v>0.46</v>
@@ -48947,7 +48947,7 @@
         <v>1</v>
       </c>
       <c r="AD512" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="513">
@@ -49032,7 +49032,7 @@
         <v>0.51</v>
       </c>
       <c r="AA513" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="AB513" t="n">
         <v>0.57</v>
@@ -49041,7 +49041,7 @@
         <v>2</v>
       </c>
       <c r="AD513" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="514">
@@ -49126,7 +49126,7 @@
         <v>0.38</v>
       </c>
       <c r="AA514" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="AB514" t="n">
         <v>0.67</v>
@@ -49135,7 +49135,7 @@
         <v>3</v>
       </c>
       <c r="AD514" t="n">
-        <v>0.5065000000000001</v>
+        <v>0.5185</v>
       </c>
     </row>
     <row r="515">
@@ -49314,7 +49314,7 @@
         <v>0.51</v>
       </c>
       <c r="AA516" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="AB516" t="n">
         <v>0.57</v>
@@ -49323,7 +49323,7 @@
         <v>2</v>
       </c>
       <c r="AD516" t="n">
-        <v>0.5950000000000001</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="517">
@@ -49408,7 +49408,7 @@
         <v>0.38</v>
       </c>
       <c r="AA517" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AB517" t="n">
         <v>0.67</v>
@@ -49417,7 +49417,7 @@
         <v>3</v>
       </c>
       <c r="AD517" t="n">
-        <v>0.4995000000000001</v>
+        <v>0.5135</v>
       </c>
     </row>
     <row r="518">
@@ -49502,7 +49502,7 @@
         <v>0.64</v>
       </c>
       <c r="AA518" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="AB518" t="n">
         <v>0.46</v>
@@ -49511,7 +49511,7 @@
         <v>1</v>
       </c>
       <c r="AD518" t="n">
-        <v>0.6639999999999999</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="519">
@@ -49596,7 +49596,7 @@
         <v>0.51</v>
       </c>
       <c r="AA519" t="n">
-        <v>0.83</v>
+        <v>0.95</v>
       </c>
       <c r="AB519" t="n">
         <v>0.57</v>
@@ -49605,7 +49605,7 @@
         <v>2</v>
       </c>
       <c r="AD519" t="n">
-        <v>0.5950000000000001</v>
+        <v>0.619</v>
       </c>
     </row>
     <row r="520">
@@ -49690,7 +49690,7 @@
         <v>0.38</v>
       </c>
       <c r="AA520" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="AB520" t="n">
         <v>0.67</v>
@@ -49699,7 +49699,7 @@
         <v>3</v>
       </c>
       <c r="AD520" t="n">
-        <v>0.5005000000000001</v>
+        <v>0.5265</v>
       </c>
     </row>
     <row r="521">
@@ -49784,7 +49784,7 @@
         <v>0.85</v>
       </c>
       <c r="AA521" t="n">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="AB521" t="n">
         <v>0.76</v>
@@ -49793,7 +49793,7 @@
         <v>1</v>
       </c>
       <c r="AD521" t="n">
-        <v>0.8295</v>
+        <v>0.8455</v>
       </c>
     </row>
     <row r="522">
@@ -49878,7 +49878,7 @@
         <v>0.77</v>
       </c>
       <c r="AA522" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
       <c r="AB522" t="n">
         <v>0.57</v>
@@ -49887,7 +49887,7 @@
         <v>2</v>
       </c>
       <c r="AD522" t="n">
-        <v>0.754</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="523">
@@ -49972,7 +49972,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA523" t="n">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="AB523" t="n">
         <v>0.67</v>
@@ -49981,7 +49981,7 @@
         <v>3</v>
       </c>
       <c r="AD523" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="524">
@@ -50066,7 +50066,7 @@
         <v>0.64</v>
       </c>
       <c r="AA524" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="AB524" t="n">
         <v>0.46</v>
@@ -50075,7 +50075,7 @@
         <v>1</v>
       </c>
       <c r="AD524" t="n">
-        <v>0.659</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="525">
@@ -50160,7 +50160,7 @@
         <v>0.51</v>
       </c>
       <c r="AA525" t="n">
-        <v>0.83</v>
+        <v>0.95</v>
       </c>
       <c r="AB525" t="n">
         <v>0.57</v>
@@ -50169,7 +50169,7 @@
         <v>2</v>
       </c>
       <c r="AD525" t="n">
-        <v>0.5920000000000001</v>
+        <v>0.616</v>
       </c>
     </row>
     <row r="526">
@@ -50254,7 +50254,7 @@
         <v>0.38</v>
       </c>
       <c r="AA526" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="AB526" t="n">
         <v>0.67</v>
@@ -50263,7 +50263,7 @@
         <v>3</v>
       </c>
       <c r="AD526" t="n">
-        <v>0.4975000000000001</v>
+        <v>0.5255</v>
       </c>
     </row>
     <row r="527">
@@ -50348,7 +50348,7 @@
         <v>0.83</v>
       </c>
       <c r="AA527" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="AB527" t="n">
         <v>0.35</v>
@@ -50357,7 +50357,7 @@
         <v>1</v>
       </c>
       <c r="AD527" t="n">
-        <v>0.6869999999999999</v>
+        <v>0.705</v>
       </c>
     </row>
     <row r="528">
@@ -50442,7 +50442,7 @@
         <v>0.64</v>
       </c>
       <c r="AA528" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="AB528" t="n">
         <v>0.46</v>
@@ -50451,7 +50451,7 @@
         <v>2</v>
       </c>
       <c r="AD528" t="n">
-        <v>0.6100000000000001</v>
+        <v>0.626</v>
       </c>
     </row>
     <row r="529">
@@ -50536,7 +50536,7 @@
         <v>0.38</v>
       </c>
       <c r="AA529" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="AB529" t="n">
         <v>0.67</v>
@@ -50545,7 +50545,7 @@
         <v>3</v>
       </c>
       <c r="AD529" t="n">
-        <v>0.4785</v>
+        <v>0.4925</v>
       </c>
     </row>
     <row r="530">
@@ -50630,7 +50630,7 @@
         <v>0.96</v>
       </c>
       <c r="AA530" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="AB530" t="n">
         <v>0.35</v>
@@ -50639,7 +50639,7 @@
         <v>2</v>
       </c>
       <c r="AD530" t="n">
-        <v>0.7775</v>
+        <v>0.7955</v>
       </c>
     </row>
     <row r="531">
@@ -50724,7 +50724,7 @@
         <v>0.85</v>
       </c>
       <c r="AA531" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="AB531" t="n">
         <v>0.76</v>
@@ -50733,7 +50733,7 @@
         <v>1</v>
       </c>
       <c r="AD531" t="n">
-        <v>0.8035</v>
+        <v>0.8195</v>
       </c>
     </row>
     <row r="532">
@@ -50818,7 +50818,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA532" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="AB532" t="n">
         <v>0.93</v>
@@ -50827,7 +50827,7 @@
         <v>3</v>
       </c>
       <c r="AD532" t="n">
-        <v>0.7370000000000001</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="533">
@@ -51297,7 +51297,7 @@
         <v>2</v>
       </c>
       <c r="AD537" t="n">
-        <v>0.7149999999999999</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="538">
@@ -51485,7 +51485,7 @@
         <v>1</v>
       </c>
       <c r="AD539" t="n">
-        <v>0.7344999999999999</v>
+        <v>0.7345</v>
       </c>
     </row>
     <row r="540">
@@ -51758,7 +51758,7 @@
         <v>0.9</v>
       </c>
       <c r="AA542" t="n">
-        <v>0.49</v>
+        <v>0.59</v>
       </c>
       <c r="AB542" t="n">
         <v>0.29</v>
@@ -51767,7 +51767,7 @@
         <v>1</v>
       </c>
       <c r="AD542" t="n">
-        <v>0.7115</v>
+        <v>0.7315</v>
       </c>
     </row>
     <row r="543">
@@ -51852,7 +51852,7 @@
         <v>0.71</v>
       </c>
       <c r="AA543" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB543" t="n">
         <v>0.31</v>
@@ -51861,7 +51861,7 @@
         <v>2</v>
       </c>
       <c r="AD543" t="n">
-        <v>0.633</v>
+        <v>0.649</v>
       </c>
     </row>
     <row r="544">
@@ -51946,7 +51946,7 @@
         <v>0.51</v>
       </c>
       <c r="AA544" t="n">
-        <v>0.84</v>
+        <v>0.98</v>
       </c>
       <c r="AB544" t="n">
         <v>0.57</v>
@@ -51955,7 +51955,7 @@
         <v>3</v>
       </c>
       <c r="AD544" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.586</v>
       </c>
     </row>
     <row r="545">
@@ -52049,7 +52049,7 @@
         <v>3</v>
       </c>
       <c r="AD545" t="n">
-        <v>0.6764999999999999</v>
+        <v>0.6765</v>
       </c>
     </row>
     <row r="546">
@@ -52143,7 +52143,7 @@
         <v>1</v>
       </c>
       <c r="AD546" t="n">
-        <v>0.8270000000000001</v>
+        <v>0.827</v>
       </c>
     </row>
     <row r="547">
@@ -52331,7 +52331,7 @@
         <v>1</v>
       </c>
       <c r="AD548" t="n">
-        <v>0.7829999999999999</v>
+        <v>0.783</v>
       </c>
     </row>
     <row r="549">
@@ -52425,7 +52425,7 @@
         <v>2</v>
       </c>
       <c r="AD549" t="n">
-        <v>0.5395000000000001</v>
+        <v>0.5395</v>
       </c>
     </row>
     <row r="550">
@@ -52604,7 +52604,7 @@
         <v>0.96</v>
       </c>
       <c r="AA551" t="n">
-        <v>0.59</v>
+        <v>0.68</v>
       </c>
       <c r="AB551" t="n">
         <v>0.35</v>
@@ -52613,7 +52613,7 @@
         <v>2</v>
       </c>
       <c r="AD551" t="n">
-        <v>0.7884999999999999</v>
+        <v>0.8065</v>
       </c>
     </row>
     <row r="552">
@@ -52698,7 +52698,7 @@
         <v>0.85</v>
       </c>
       <c r="AA552" t="n">
-        <v>0.82</v>
+        <v>0.89</v>
       </c>
       <c r="AB552" t="n">
         <v>0.76</v>
@@ -52707,7 +52707,7 @@
         <v>1</v>
       </c>
       <c r="AD552" t="n">
-        <v>0.8245</v>
+        <v>0.8385</v>
       </c>
     </row>
     <row r="553">
@@ -52792,7 +52792,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AA553" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AB553" t="n">
         <v>0.67</v>
@@ -52801,7 +52801,7 @@
         <v>3</v>
       </c>
       <c r="AD553" t="n">
-        <v>0.7170000000000001</v>
+        <v>0.731</v>
       </c>
     </row>
     <row r="554">
@@ -53083,7 +53083,7 @@
         <v>3</v>
       </c>
       <c r="AD556" t="n">
-        <v>0.5455000000000001</v>
+        <v>0.5455</v>
       </c>
     </row>
     <row r="557">
@@ -53168,7 +53168,7 @@
         <v>0.83</v>
       </c>
       <c r="AA557" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="AB557" t="n">
         <v>0.5</v>
@@ -53177,7 +53177,7 @@
         <v>1</v>
       </c>
       <c r="AD557" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.7685</v>
       </c>
     </row>
     <row r="558">
@@ -53262,7 +53262,7 @@
         <v>0.72</v>
       </c>
       <c r="AA558" t="n">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="AB558" t="n">
         <v>0.46</v>
@@ -53271,7 +53271,7 @@
         <v>2</v>
       </c>
       <c r="AD558" t="n">
-        <v>0.7030000000000001</v>
+        <v>0.719</v>
       </c>
     </row>
     <row r="559">
@@ -53356,7 +53356,7 @@
         <v>0.62</v>
       </c>
       <c r="AA559" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
       <c r="AB559" t="n">
         <v>0.57</v>
@@ -53365,7 +53365,7 @@
         <v>3</v>
       </c>
       <c r="AD559" t="n">
-        <v>0.6565000000000001</v>
+        <v>0.6825</v>
       </c>
     </row>
     <row r="560">
@@ -53450,7 +53450,7 @@
         <v>0.74</v>
       </c>
       <c r="AA560" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="AB560" t="n">
         <v>0.46</v>
@@ -53459,7 +53459,7 @@
         <v>1</v>
       </c>
       <c r="AD560" t="n">
-        <v>0.7210000000000001</v>
+        <v>0.737</v>
       </c>
     </row>
     <row r="561">
@@ -53544,7 +53544,7 @@
         <v>0.64</v>
       </c>
       <c r="AA561" t="n">
-        <v>0.83</v>
+        <v>0.95</v>
       </c>
       <c r="AB561" t="n">
         <v>0.57</v>
@@ -53553,7 +53553,7 @@
         <v>2</v>
       </c>
       <c r="AD561" t="n">
-        <v>0.6735</v>
+        <v>0.6975</v>
       </c>
     </row>
     <row r="562">
@@ -53638,7 +53638,7 @@
         <v>0.54</v>
       </c>
       <c r="AA562" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="AB562" t="n">
         <v>0.67</v>
@@ -53647,7 +53647,7 @@
         <v>3</v>
       </c>
       <c r="AD562" t="n">
-        <v>0.5955</v>
+        <v>0.6235000000000001</v>
       </c>
     </row>
     <row r="563">
@@ -53929,7 +53929,7 @@
         <v>3</v>
       </c>
       <c r="AD565" t="n">
-        <v>0.7509999999999999</v>
+        <v>0.751</v>
       </c>
     </row>
     <row r="566">
@@ -54023,7 +54023,7 @@
         <v>3</v>
       </c>
       <c r="AD566" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="567">
@@ -54211,7 +54211,7 @@
         <v>1</v>
       </c>
       <c r="AD568" t="n">
-        <v>0.8624999999999999</v>
+        <v>0.8625</v>
       </c>
     </row>
     <row r="569">
@@ -54493,7 +54493,7 @@
         <v>3</v>
       </c>
       <c r="AD571" t="n">
-        <v>0.7609999999999999</v>
+        <v>0.761</v>
       </c>
     </row>
     <row r="572">
@@ -54681,7 +54681,7 @@
         <v>1</v>
       </c>
       <c r="AD573" t="n">
-        <v>0.7825000000000001</v>
+        <v>0.7825</v>
       </c>
     </row>
     <row r="574">
@@ -54869,7 +54869,7 @@
         <v>3</v>
       </c>
       <c r="AD575" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="576">
@@ -54963,7 +54963,7 @@
         <v>2</v>
       </c>
       <c r="AD576" t="n">
-        <v>0.8164999999999999</v>
+        <v>0.8165</v>
       </c>
     </row>
     <row r="577">
@@ -55142,7 +55142,7 @@
         <v>1</v>
       </c>
       <c r="AA578" t="n">
-        <v>0.49</v>
+        <v>0.59</v>
       </c>
       <c r="AB578" t="n">
         <v>0.29</v>
@@ -55151,7 +55151,7 @@
         <v>3</v>
       </c>
       <c r="AD578" t="n">
-        <v>0.7794999999999999</v>
+        <v>0.7995</v>
       </c>
     </row>
     <row r="579">
@@ -55236,16 +55236,16 @@
         <v>0.92</v>
       </c>
       <c r="AA579" t="n">
-        <v>0.65</v>
+        <v>0.74</v>
       </c>
       <c r="AB579" t="n">
         <v>0.5</v>
       </c>
       <c r="AC579" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD579" t="n">
-        <v>0.7879999999999999</v>
+        <v>0.806</v>
       </c>
     </row>
     <row r="580">
@@ -55330,16 +55330,16 @@
         <v>0.77</v>
       </c>
       <c r="AA580" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="AB580" t="n">
         <v>0.85</v>
       </c>
       <c r="AC580" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD580" t="n">
-        <v>0.7909999999999999</v>
+        <v>0.803</v>
       </c>
     </row>
     <row r="581">
@@ -55433,7 +55433,7 @@
         <v>3</v>
       </c>
       <c r="AD581" t="n">
-        <v>0.8074999999999999</v>
+        <v>0.8075</v>
       </c>
     </row>
     <row r="582">
@@ -55527,7 +55527,7 @@
         <v>1</v>
       </c>
       <c r="AD582" t="n">
-        <v>0.8170000000000001</v>
+        <v>0.8169999999999999</v>
       </c>
     </row>
     <row r="583">
@@ -55621,7 +55621,7 @@
         <v>2</v>
       </c>
       <c r="AD583" t="n">
-        <v>0.8139999999999998</v>
+        <v>0.8139999999999999</v>
       </c>
     </row>
     <row r="584">
@@ -55715,7 +55715,7 @@
         <v>3</v>
       </c>
       <c r="AD584" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.785</v>
       </c>
     </row>
     <row r="585">
